--- a/docs/design/行为事件表.xlsx
+++ b/docs/design/行为事件表.xlsx
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>未开工：2026-10-10 新定，取代已删除的「打听」（ask_about）</t>
+          <t>已实装：observe_behavior.gd + 内核 do_observe；本版只做单人对象，信息在提交时即交付</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -20077,7 +20077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -20117,7 +20117,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>全部效果行（47 条）</t>
+          <t>全部效果行（39 条）</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -21796,7 +21796,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ask_help_cost_stress</t>
+          <t>apologize_cost_stress</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -21806,12 +21806,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -21836,32 +21836,36 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>求助发起成本：开口求人本身有压力（不论成败）</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr"/>
+          <t>道歉发起成本：主动低头本身有压力</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>apologize</t>
+        </is>
+      </c>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ask_help_ok_asker_affinity</t>
+          <t>apologize_ok_hostility</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>hostility</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -21876,14 +21880,14 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
           <t>normal</t>
@@ -21891,37 +21895,41 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>求助成功：求助者对帮忙者好感↑</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr"/>
+          <t>道歉被接受：**只消表层**敌对（心结 H_deep 不因道歉而消，§10.22）</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>apologize</t>
+        </is>
+      </c>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ask_help_ok_asker_stress</t>
+          <t>apologize_ok_affinity</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -21946,27 +21954,31 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>求助成功：求助者压力↓</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr"/>
+          <t>道歉被接受：好感回升（双向）</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>apologize</t>
+        </is>
+      </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ask_help_ok_helper_affinity</t>
+          <t>apologize_ok_trust</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -21986,7 +21998,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -22001,32 +22013,36 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>求助成功：帮忙者对求助者好感↑</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr"/>
+          <t>道歉被接受：信任回升（双向）</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>apologize</t>
+        </is>
+      </c>
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ask_help_ok_helper_trust</t>
+          <t>apologize_ok_stress</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -22041,7 +22057,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -22056,54 +22072,58 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>求助成功：帮忙者对求助者信任↑</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr"/>
+          <t>道歉被接受：双方都松口气</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>apologize</t>
+        </is>
+      </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ask_help_no_stress</t>
+          <t>apologize_no_hostility</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>hostility</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
           <t>normal</t>
@@ -22111,32 +22131,36 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>求助被拒：求助者压力↑</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr"/>
+          <t>道歉被拒：敌对继续累积（表层的，不写深层）</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>apologize</t>
+        </is>
+      </c>
       <c r="L36" s="6" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>ask_help_no_hostility</t>
+          <t>apologize_no_stress</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>hostility</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -22151,37 +22175,41 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>major</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>求助被拒：求助者转而生恨</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr"/>
+          <t>道歉被拒：主动低头被驳回（重大档）</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>apologize</t>
+        </is>
+      </c>
       <c r="L37" s="6" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ask_help_no_trust</t>
+          <t>apologize_no_trust</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -22221,32 +22249,36 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>求助被拒：信任受损</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr"/>
+          <t>道歉被拒：信任受损</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>apologize</t>
+        </is>
+      </c>
       <c r="L38" s="6" t="inlineStr"/>
       <c r="M38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>apologize_cost_stress</t>
+          <t>note_bad_to_hostile</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>hostility</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -22261,12 +22293,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -22276,26 +22308,22 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>道歉发起成本：主动低头本身有压力</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
+          <t>纸条坏话：本就讨厌被说者 → 敌对 +1</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="6" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>apologize_ok_hostility</t>
+          <t>note_good_to_hostile</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -22305,7 +22333,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -22320,12 +22348,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -22335,26 +22363,22 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>道歉被接受：**只消表层**敌对（心结 H_deep 不因道歉而消，§10.22）</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
+          <t>纸条好话：讨厌被说者 → 敌对 −1（稍微松动）</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr"/>
       <c r="L40" s="6" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>apologize_ok_affinity</t>
+          <t>note_good_to_friendly</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -22364,7 +22388,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -22394,36 +22418,32 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>道歉被接受：好感回升（双向）</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
+          <t>纸条好话：喜欢被说者 → 好感 +1</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>apologize_ok_trust</t>
+          <t>note_bad_to_friendly</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -22438,7 +22458,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -22453,235 +22473,124 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>道歉被接受：信任回升（双向）</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
+          <t>纸条坏话：喜欢被说者 → 好感 −1（开始动摇）</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="6" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr"/>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>apologize_ok_stress</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>道歉被接受：双方都松口气</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="L43" s="6" t="inlineStr"/>
-      <c r="M43" s="6" t="inlineStr"/>
-    </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>apologize_no_hostility</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>hostility</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>道歉被拒：敌对继续累积（表层的，不写深层）</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="L44" s="6" t="inlineStr"/>
-      <c r="M44" s="6" t="inlineStr"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>P0 待创建效果行（尚未落 data/balance/w_events.csv；来源 §17.2.5、§17.3.5）</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>apologize_no_stress</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>道歉被拒：主动低头被驳回（重大档）</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr"/>
-      <c r="M45" s="6" t="inlineStr"/>
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>w_e</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>w_s</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>w_f</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>w_j</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>归属行为</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>新值／改动（填写）</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>备注（填写）</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>apologize_no_trust</t>
+          <t>teacher_visit_stress</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr">
         <is>
           <t>normal</t>
@@ -22689,17 +22598,17 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>道歉被拒：信任受损</t>
+          <t>老师巡查到场：全班压力 +3（豁免 睡觉 / 正在学习 / 出门）</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>apologize</t>
+          <t>teacher_patrol</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr"/>
@@ -22708,39 +22617,23 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>note_bad_to_hostile</t>
+          <t>leave_absence</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>hostility</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
           <t>normal</t>
@@ -22748,54 +22641,42 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>纸条坏话：本就讨厌被说者 → 敌对 +1</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr"/>
+          <t>出门：8 邻域邻居对玩家好感 −3（常规档上限）</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>leave_class</t>
+        </is>
+      </c>
       <c r="L47" s="6" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>note_good_to_hostile</t>
+          <t>study_stress</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>hostility</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr">
         <is>
           <t>normal</t>
@@ -22803,27 +22684,31 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>纸条好话：讨厌被说者 → 敌对 −1（稍微松动）</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr"/>
+          <t>学习每 10 tick 结算：本人压力 +3（本次调整，改造原涓流 +1/每天 2 次）</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
       <c r="L48" s="6" t="inlineStr"/>
       <c r="M48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>note_good_to_friendly</t>
+          <t>study_together_trust</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -22831,26 +22716,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr">
         <is>
           <t>normal</t>
@@ -22863,17 +22732,21 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>纸条好话：喜欢被说者 → 好感 +1</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr"/>
+          <t>学习圈每 20 tick：双向信任 +1（替换 v4 §2.3 的「每天 2 次 A+1/T+1」）</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>study（学习圈）</t>
+        </is>
+      </c>
       <c r="L49" s="6" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>note_bad_to_friendly</t>
+          <t>study_together_affinity</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -22883,29 +22756,13 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr">
         <is>
           <t>normal</t>
@@ -22918,399 +22775,102 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>纸条坏话：喜欢被说者 → 好感 −1（开始动摇）</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr"/>
+          <t>学习圈每 20 tick：双向好感 +1</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>study（学习圈）</t>
+        </is>
+      </c>
       <c r="L50" s="6" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>study_together_stress</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>学习圈每 20 tick：本人压力 +1</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>study（学习圈）</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr"/>
+    </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>P0 待创建效果行（尚未落 data/balance/w_events.csv；来源 §17.2.5、§17.3.5）</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>axis</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>w_e</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>w_s</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>w_f</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>w_j</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>归属行为</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>新值／改动（填写）</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>备注（填写）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>teacher_visit_stress</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>reject_stress（复用现有键）</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>stress</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>老师巡查到场：全班压力 +3（豁免 睡觉 / 正在学习 / 出门）</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>teacher_patrol</t>
-        </is>
-      </c>
-      <c r="L54" s="6" t="inlineStr"/>
-      <c r="M54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>leave_absence</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>affinity</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>出门：8 邻域邻居对玩家好感 −3（常规档上限）</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>leave_class</t>
-        </is>
-      </c>
-      <c r="L55" s="6" t="inlineStr"/>
-      <c r="M55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>study_stress</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>学习每 10 tick 结算：本人压力 +3（本次调整，改造原涓流 +1/每天 2 次）</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>拒绝学习邀请：发起者压力 +2（复用现有 reject_stress，不新建键）</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="L56" s="6" t="inlineStr"/>
-      <c r="M56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>study_together_trust</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>学习圈每 20 tick：双向信任 +1（替换 v4 §2.3 的「每天 2 次 A+1/T+1」）</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>study（学习圈）</t>
-        </is>
-      </c>
-      <c r="L57" s="6" t="inlineStr"/>
-      <c r="M57" s="6" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>study_together_affinity</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>affinity</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>学习圈每 20 tick：双向好感 +1</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>study（学习圈）</t>
-        </is>
-      </c>
-      <c r="L58" s="6" t="inlineStr"/>
-      <c r="M58" s="6" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>study_together_stress</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>学习圈每 20 tick：本人压力 +1</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>study（学习圈）</t>
-        </is>
-      </c>
-      <c r="L59" s="6" t="inlineStr"/>
-      <c r="M59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>reject_stress（复用现有键）</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>拒绝学习邀请：发起者压力 +2（复用现有 reject_stress，不新建键）</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>study</t>
-        </is>
-      </c>
-      <c r="L60" s="6" t="inlineStr"/>
-      <c r="M60" s="6" t="inlineStr"/>
+      <c r="L52" s="6" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23323,7 +22883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23347,7 +22907,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>全部参数（20 条）</t>
+          <t>全部参数（19 条）</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -23651,17 +23211,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>ask_help_p</t>
+          <t>apologize_p</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>求助：每 tick 触发概率（仅在「我对目标好感 ≥ 门槛」时才可能命中）</t>
+          <t>道歉：每 tick 触发概率（仅在「我对他敌对 ≥30 且以为他也敌对」时才可能命中；属**窄条件**行为）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
@@ -23670,17 +23230,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>apologize_p</t>
+          <t>report_p</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>道歉：每 tick 触发概率（仅在「我对他敌对 ≥30 且以为他也敌对」时才可能命中；属**窄条件**行为）</t>
+          <t>举报：每段课间对有把柄候选掷骰一次的概率上限（实际 = report_p × σ(z)）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -23689,17 +23249,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>report_p</t>
+          <t>phone_expose_p</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>举报：每段课间对有把柄候选掷骰一次的概率上限（实际 = report_p × σ(z)）</t>
+          <t>带手机者每课间段被目击到玩手机的概率（产生举报把柄；仅课间段）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -23708,17 +23268,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>phone_expose_p</t>
+          <t>burst_p_max</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>带手机者每课间段被目击到玩手机的概率（产生举报把柄；仅课间段）</t>
+          <t>压力爆发：满压（stress=100）时的日爆发概率；实际 p = burst_p_max × (stress−theta)/(100−theta)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -23727,40 +23287,21 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>burst_p_max</t>
+          <t>study</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>压力爆发：满压（stress=100）时的日爆发概率；实际 p = burst_p_max × (stress−theta)/(100−theta)</t>
+          <t>学习（默认行为：无主行为且未走动时自动进入）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>study</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>学习（默认行为：无主行为且未走动时自动进入）</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23773,7 +23314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -23801,7 +23342,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>全部门槛（43 条）</t>
+          <t>全部门槛（37 条）</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -24808,12 +24349,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>ask_help</t>
+          <t>apologize</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>accept_theta</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -24823,12 +24364,12 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>求助：好感门槛默认值（E = 50）</t>
+          <t>道歉判定：被接受的 sigmoid 拐点</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -24837,12 +24378,12 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ask_help</t>
+          <t>apologize</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>introvert_affinity</t>
+          <t>accept_scale</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -24852,12 +24393,12 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>求助：好感门槛的内向端（E=0）</t>
+          <t>道歉判定 sigmoid 坡度</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr"/>
@@ -24866,12 +24407,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>ask_help</t>
+          <t>apologize</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>extrovert_affinity</t>
+          <t>calm_bonus</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -24886,7 +24427,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>求助：好感门槛的外向端（E=100）</t>
+          <t>道歉判定：对方随和系数（F_j/100 × 此值，§10.11「对方随和系数」）</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -24895,12 +24436,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>ask_help</t>
+          <t>apologize</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>accept_theta</t>
+          <t>hostility_penalty</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -24910,190 +24451,16 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>求助判定：被接纳的 sigmoid 拐点（score = A[j][i] + 对方外向度加成）</t>
+          <t>道歉判定：对方敌对对接受概率的压制（§10.11「− 敌对值 ×0.5」）</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
       <c r="G40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>ask_help</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>accept_scale</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>求助判定 sigmoid 坡度（越大越缓）</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr"/>
-      <c r="G41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>ask_help</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>extrovert_bonus</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>求助判定：被求助者外向度加成上限（E_j/100 × 此值）</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>accept_theta</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>道歉判定：被接受的 sigmoid 拐点</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr"/>
-      <c r="G43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>accept_scale</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>道歉判定 sigmoid 坡度</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr"/>
-      <c r="G44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>calm_bonus</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>道歉判定：对方随和系数（F_j/100 × 此值，§10.11「对方随和系数」）</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr"/>
-      <c r="G45" s="6" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>hostility_penalty</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>道歉判定：对方敌对对接受概率的压制（§10.11「− 敌对值 ×0.5」）</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr"/>
-      <c r="G46" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -34126,7 +33493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>现状：未开工（2026-10-10 新定；取代已删除的「打听」） ｜ 只读列不要改；请在「新值／改动（填写）」列写本次大调整</t>
+          <t>现状：已实装（2026-10-10：单人对象；群体观察待做） ｜ 只读列不要改；请在「新值／改动（填写）」列写本次大调整</t>
         </is>
       </c>
     </row>
@@ -34181,7 +33548,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>P0 规格（待落 behaviors.csv）</t>
+          <t>behaviors.csv</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
@@ -34200,7 +33567,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>P0 规格</t>
+          <t>behaviors.csv</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
@@ -34252,7 +33619,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>未开工：2026-10-10 新定，取代已删除的「打听」</t>
+          <t>已实装（2026-10-10）：取代已删除的「打听」；本版只做单人对象</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -34290,7 +33657,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>（无实现）需新增玩家行为 + 只读信息接口</t>
+          <t>scripts/systems/behaviors/observe_behavior.gd；内核 `player_action("observe", target)` / `do_observe`</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -35372,12 +34739,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>对象离开范围或活动结束 → 观察结束；已读到的信息是否交付**待裁定**</t>
+          <t>本版：观察在**提交时即交付**信息（散步快照），中途中断不回滚；后续可改为「走完才交付」</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>待裁定</t>
+          <t>本版</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr"/>
@@ -35561,12 +34928,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>同一对象连续观察是否设冷却**待裁定**</t>
+          <t>无冷却（§10.3.1：无次数限制，仅受课间时间预算约束）</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>待裁定</t>
+          <t>本版</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr"/>

--- a/docs/design/行为事件表.xlsx
+++ b/docs/design/行为事件表.xlsx
@@ -9612,7 +9612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>现状：已实现（段粒度判定；内核 _roll_sleep / _settle_sleep） ｜ 只读列不要改；请在「新值／改动（填写）」列写本次大调整</t>
+          <t>现状：已实现（NPC 概率触发 + 玩家主动；内核 _roll_sleep / _settle_sleep） ｜ 只读列不要改；请在「新值／改动（填写）」列写本次大调整</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -20117,7 +20117,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>全部效果行（39 条）</t>
+          <t>全部效果行（40 条）</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -22485,149 +22485,161 @@
       <c r="L42" s="6" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>study_stress</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>主动学习：每满一档给自身压力 +3（§8.23）</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>P0 待创建效果行（尚未落 data/balance/w_events.csv；来源 §17.2.5、§17.3.5）</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
-      <c r="M44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>base</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>w_e</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>w_s</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>w_f</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>w_j</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>归属行为</t>
         </is>
       </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>新值／改动（填写）</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>备注（填写）</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>teacher_visit_stress</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>老师巡查到场：全班压力 +3（豁免 睡觉 / 正在学习 / 出门）</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>teacher_patrol</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr"/>
-      <c r="M46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>leave_absence</t>
+          <t>teacher_visit_stress</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr"/>
@@ -22646,12 +22658,12 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>出门：8 邻域邻居对玩家好感 −3（常规档上限）</t>
+          <t>老师巡查到场：全班压力 +3（豁免 睡觉 / 正在学习 / 出门）</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>leave_class</t>
+          <t>teacher_patrol</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
@@ -22660,17 +22672,17 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>study_stress</t>
+          <t>leave_absence</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr"/>
@@ -22684,17 +22696,17 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>学习每 10 tick 结算：本人压力 +3（本次调整，改造原涓流 +1/每天 2 次）</t>
+          <t>出门：8 邻域邻居对玩家好感 −3（常规档上限）</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>leave_class</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -22703,17 +22715,17 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>study_together_trust</t>
+          <t>study_stress</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr"/>
@@ -22732,12 +22744,12 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>学习圈每 20 tick：双向信任 +1（替换 v4 §2.3 的「每天 2 次 A+1/T+1」）</t>
+          <t>学习每 10 tick 结算：本人压力 +3（本次调整，改造原涓流 +1/每天 2 次）</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>study（学习圈）</t>
+          <t>study</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -22746,12 +22758,12 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>study_together_affinity</t>
+          <t>study_together_trust</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -22775,7 +22787,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>学习圈每 20 tick：双向好感 +1</t>
+          <t>学习圈每 20 tick：双向信任 +1（替换 v4 §2.3 的「每天 2 次 A+1/T+1」）</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -22789,12 +22801,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>study_together_stress</t>
+          <t>study_together_affinity</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -22818,7 +22830,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>学习圈每 20 tick：本人压力 +1</t>
+          <t>学习圈每 20 tick：双向好感 +1</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -22832,7 +22844,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>reject_stress（复用现有键）</t>
+          <t>study_together_stress</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -22842,7 +22854,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
@@ -22856,21 +22868,64 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>拒绝学习邀请：发起者压力 +2（复用现有 reject_stress，不新建键）</t>
+          <t>学习圈每 20 tick：本人压力 +1</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>study（学习圈）</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr"/>
       <c r="M52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>reject_stress（复用现有键）</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>拒绝学习邀请：发起者压力 +2（复用现有 reject_stress，不新建键）</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28872,7 +28927,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>现状：待重构（现行 = 默认状态；目标 = 主动行为） ｜ 只读列不要改；请在「新值／改动（填写）」列写本次大调整</t>
+          <t>现状：已实装玩家侧（2026-10-10；NPC 侧仍是「空闲即在学」） ｜ 只读列不要改；请在「新值／改动（填写）」列写本次大调整</t>
         </is>
       </c>
     </row>

--- a/docs/design/行为事件表.xlsx
+++ b/docs/design/行为事件表.xlsx
@@ -20077,7 +20077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -20117,7 +20117,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>全部效果行（40 条）</t>
+          <t>全部效果行（43 条）</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -22540,235 +22540,271 @@
       <c r="L43" s="6" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>study_circle_trust</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>学习圈每 20 tick：双向信任 +1（§8.23 第 4 条）</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr"/>
+    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>study_circle_affinity</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>affinity</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>学习圈每 20 tick：双向好感 +1</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>study_circle_stress</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>学习圈每 20 tick：自身压力 +1（每人只算一次）</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>P0 待创建效果行（尚未落 data/balance/w_events.csv；来源 §17.2.5、§17.3.5）</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>base</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>w_e</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>w_s</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>w_f</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>w_j</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>归属行为</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>新值／改动（填写）</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>备注（填写）</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>teacher_visit_stress</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>老师巡查到场：全班压力 +3（豁免 睡觉 / 正在学习 / 出门）</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>teacher_patrol</t>
-        </is>
-      </c>
-      <c r="L47" s="6" t="inlineStr"/>
-      <c r="M47" s="6" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>leave_absence</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>affinity</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>出门：8 邻域邻居对玩家好感 −3（常规档上限）</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>leave_class</t>
-        </is>
-      </c>
-      <c r="L48" s="6" t="inlineStr"/>
-      <c r="M48" s="6" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>study_stress</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>学习每 10 tick 结算：本人压力 +3（本次调整，改造原涓流 +1/每天 2 次）</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>study</t>
-        </is>
-      </c>
-      <c r="L49" s="6" t="inlineStr"/>
-      <c r="M49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>study_together_trust</t>
+          <t>teacher_visit_stress</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
@@ -22782,17 +22818,17 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>学习圈每 20 tick：双向信任 +1（替换 v4 §2.3 的「每天 2 次 A+1/T+1」）</t>
+          <t>老师巡查到场：全班压力 +3（豁免 睡觉 / 正在学习 / 出门）</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>study（学习圈）</t>
+          <t>teacher_patrol</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
@@ -22801,7 +22837,7 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>study_together_affinity</t>
+          <t>leave_absence</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -22811,7 +22847,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr"/>
@@ -22825,17 +22861,17 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>学习圈每 20 tick：双向好感 +1</t>
+          <t>出门：8 邻域邻居对玩家好感 −3（常规档上限）</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>study（学习圈）</t>
+          <t>leave_class</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr"/>
@@ -22844,7 +22880,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>study_together_stress</t>
+          <t>study_stress</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -22854,7 +22890,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
@@ -22873,12 +22909,12 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>学习圈每 20 tick：本人压力 +1</t>
+          <t>学习每 10 tick 结算：本人压力 +3（本次调整，改造原涓流 +1/每天 2 次）</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>study（学习圈）</t>
+          <t>study</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr"/>
@@ -22887,17 +22923,17 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>reject_stress（复用现有键）</t>
+          <t>study_together_trust</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr"/>
@@ -22911,21 +22947,150 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>拒绝学习邀请：发起者压力 +2（复用现有 reject_stress，不新建键）</t>
+          <t>学习圈每 20 tick：双向信任 +1（替换 v4 §2.3 的「每天 2 次 A+1/T+1」）</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>study（学习圈）</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr"/>
       <c r="M53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>study_together_affinity</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>affinity</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>学习圈每 20 tick：双向好感 +1</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>study（学习圈）</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>study_together_stress</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>学习圈每 20 tick：本人压力 +1</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>study（学习圈）</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr"/>
+      <c r="M55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>reject_stress（复用现有键）</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>拒绝学习邀请：发起者压力 +2（复用现有 reject_stress，不新建键）</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr"/>
+      <c r="M56" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22938,7 +23103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22962,7 +23127,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>全部参数（19 条）</t>
+          <t>全部参数（20 条）</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -23000,17 +23165,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>study_p</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>闲聊（每 tick；相邻时 ×1.5，压力≥70 时 ×0.5）</t>
+          <t>学习：每 tick 触发概率（§8.23 主动行为；标定起点待定）</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr"/>
@@ -23019,17 +23184,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>move</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>走动（段首与 50 秒后各判定一次；乘外向修正；16 NPC 理想条件下平均约 6 人至少离座一次）</t>
+          <t>闲聊（每 tick；相邻时 ×1.5，压力≥70 时 ×0.5）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr"/>
@@ -23038,17 +23203,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>neighbor_pick_mult</t>
+          <t>move</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>空间层：邻居被选为交互目标的权重倍数（§10.15 相邻修正）</t>
+          <t>走动（段首与 50 秒后各判定一次；乘外向修正；16 NPC 理想条件下平均约 6 人至少离座一次）</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
@@ -23057,17 +23222,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>free_join_rate</t>
+          <t>neighbor_pick_mult</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>「跟着做」概率：free 类活动被邻居跟随的基础概率（再乘从众度）</t>
+          <t>空间层：邻居被选为交互目标的权重倍数（§10.15 相邻修正）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
@@ -23076,17 +23241,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>sleep_relief</t>
+          <t>free_join_rate</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>睡觉：课间结束时一次性减压幅度（§10.8）</t>
+          <t>「跟着做」概率：free 类活动被邻居跟随的基础概率（再乘从众度）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
@@ -23095,17 +23260,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>sleep</t>
+          <t>sleep_relief</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>睡觉（压力≥70 时 ×1.5）</t>
+          <t>睡觉：课间结束时一次性减压幅度（§10.8）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
@@ -23114,7 +23279,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>pass_note</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -23124,7 +23289,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>传纸条：每 tick 触发概率（2026-10-10 改为独立行为；标定起点待定）</t>
+          <t>睡觉（压力≥70 时 ×1.5）</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
@@ -23133,17 +23298,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>study_stress</t>
+          <t>pass_note</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>涓流：默认学习时每次结算压力 +1（每天 2 次）</t>
+          <t>传纸条：每 tick 触发概率（2026-10-10 改为独立行为；标定起点待定）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
@@ -23152,17 +23317,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>alone_stress</t>
+          <t>study_stress</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>涓流：独处（未参与任何互动）时每次结算压力 −2</t>
+          <t>涓流：默认学习时每次结算压力 +1（每天 2 次）</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
@@ -23171,17 +23336,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>interrupted_stress</t>
+          <t>alone_stress</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>行为被相位切换打断时的压力代价（"话说到一半上课铃响了"；2.0 时打断过密会使爆发超量）</t>
+          <t>涓流：独处（未参与任何互动）时每次结算压力 −2</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
@@ -23190,17 +23355,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>tease_p</t>
+          <t>interrupted_stress</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>当众调侃：每 tick 触发概率（原硬编码在 core_sim 内）</t>
+          <t>行为被相位切换打断时的压力代价（"话说到一半上课铃响了"；2.0 时打断过密会使爆发超量）</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
@@ -23209,17 +23374,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>roughhouse_p</t>
+          <t>tease_p</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>追逐打闹：每 tick 触发概率</t>
+          <t>当众调侃：每 tick 触发概率（原硬编码在 core_sim 内）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -23228,17 +23393,17 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>exclude_p</t>
+          <t>roughhouse_p</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>排挤：每 tick 判定概率</t>
+          <t>追逐打闹：每 tick 触发概率</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
@@ -23247,17 +23412,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>comfort_p</t>
+          <t>exclude_p</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>安慰：每 tick 触发概率（命中条件本身极窄：有人压力 ≥70 + 我与他够近 + 我此刻空闲；故给出「机会来临时基本会行动」的高概率）</t>
+          <t>排挤：每 tick 判定概率</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
@@ -23266,17 +23431,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>apologize_p</t>
+          <t>comfort_p</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>道歉：每 tick 触发概率（仅在「我对他敌对 ≥30 且以为他也敌对」时才可能命中；属**窄条件**行为）</t>
+          <t>安慰：每 tick 触发概率（命中条件本身极窄：有人压力 ≥70 + 我与他够近 + 我此刻空闲；故给出「机会来临时基本会行动」的高概率）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
@@ -23285,17 +23450,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>report_p</t>
+          <t>apologize_p</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>举报：每段课间对有把柄候选掷骰一次的概率上限（实际 = report_p × σ(z)）</t>
+          <t>道歉：每 tick 触发概率（仅在「我对他敌对 ≥30 且以为他也敌对」时才可能命中；属**窄条件**行为）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -23304,17 +23469,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>phone_expose_p</t>
+          <t>report_p</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>带手机者每课间段被目击到玩手机的概率（产生举报把柄；仅课间段）</t>
+          <t>举报：每段课间对有把柄候选掷骰一次的概率上限（实际 = report_p × σ(z)）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -23323,17 +23488,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>burst_p_max</t>
+          <t>phone_expose_p</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>压力爆发：满压（stress=100）时的日爆发概率；实际 p = burst_p_max × (stress−theta)/(100−theta)</t>
+          <t>带手机者每课间段被目击到玩手机的概率（产生举报把柄；仅课间段）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -23342,21 +23507,40 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>burst_p_max</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>学习（默认行为：无主行为且未走动时自动进入）</t>
+          <t>压力爆发：满压（stress=100）时的日爆发概率；实际 p = burst_p_max × (stress−theta)/(100−theta)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>学习（默认行为：无主行为且未走动时自动进入）</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24528,7 +24712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -24682,12 +24866,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>seated_chat_range_m</t>
+          <t>seat_zone_radius_m</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -24697,7 +24881,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>同列前后紧邻且都在本座位时允许转身聊天的距离上限</t>
+          <t>自己座位的范围半径：只有在这个范围内才算「在自己的座位上」（§8.23 学习等行为的硬前置）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
@@ -24706,12 +24890,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>range_step_m</t>
+          <t>seated_chat_range_m</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -24721,7 +24905,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>连线阻挡判定采样步长（短连接段不得穿过桌椅）</t>
+          <t>同列前后紧邻且都在本座位时允许转身聊天的距离上限</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -24730,18 +24914,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>clue_opacity_split</t>
+          <t>range_step_m</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr"/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>透明度分界：闲聊对象 O &lt; 该值透露 1 条，O ≥ 该值透露 2 条（§10.5）</t>
+          <t>连线阻挡判定采样步长（短连接段不得穿过桌椅）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
@@ -24750,22 +24938,18 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>clue_count_low</t>
+          <t>clue_opacity_split</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>条</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>低透明度时透露的线索条数</t>
+          <t>透明度分界：闲聊对象 O &lt; 该值透露 1 条，O ≥ 该值透露 2 条（§10.5）</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
@@ -24774,12 +24958,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>clue_count_high</t>
+          <t>clue_count_low</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -24789,7 +24973,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>高透明度时透露的线索条数</t>
+          <t>低透明度时透露的线索条数</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
@@ -24798,7 +24982,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>actor_pick_layer</t>
+          <t>clue_count_high</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -24806,10 +24990,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>条</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>人物拾取体所在 3D 物理层（位掩码；地面点击不进这一层）</t>
+          <t>高透明度时透露的线索条数</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
@@ -24818,111 +25006,102 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>world_pick_blocker_layer</t>
+          <t>actor_pick_layer</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>世界静态遮挡体所在 3D 物理层（桌椅 / 墙；挡住人物则不可选中）</t>
+          <t>人物拾取体所在 3D 物理层（位掩码；地面点击不进这一层）</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
       <c r="F13" s="6" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>world_pick_blocker_layer</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>世界静态遮挡体所在 3D 物理层（桌椅 / 墙；挡住人物则不可选中）</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>座位表（空间层） —— data/rules/seats.csv</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>seat_id</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>row</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>col</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>新值／改动（填写）</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>备注（填写）</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>desk_side</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>讲桌旁：老师眼皮底下，邻居仅第一排 3 人</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -24932,12 +25111,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>grid</t>
+          <t>desk_side</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>第一排</t>
+          <t>讲桌旁：老师眼皮底下，邻居仅第一排 3 人</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
@@ -24946,7 +25125,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -24956,7 +25135,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -24975,7 +25154,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -24985,7 +25164,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -25004,7 +25183,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -25014,7 +25193,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -25033,17 +25212,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -25051,14 +25230,18 @@
           <t>grid</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>第一排</t>
+        </is>
+      </c>
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -25068,7 +25251,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -25083,7 +25266,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -25093,7 +25276,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -25108,7 +25291,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -25118,7 +25301,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -25133,17 +25316,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -25158,7 +25341,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -25168,7 +25351,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -25183,7 +25366,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -25193,7 +25376,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -25208,7 +25391,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -25218,7 +25401,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -25233,17 +25416,17 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -25251,18 +25434,14 @@
           <t>grid</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>最后一排</t>
-        </is>
-      </c>
+      <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr"/>
       <c r="G30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -25272,7 +25451,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -25291,7 +25470,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -25301,7 +25480,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -25320,7 +25499,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -25330,7 +25509,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -25346,67 +25525,77 @@
       <c r="F33" s="6" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr"/>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>grid</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>最后一排</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>站立点（空闲站立位置） —— data/rules/stand_points.csv</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>point_id</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>新值／改动（填写）</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>备注（填写）</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>AISLE_R1_C1</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>aisle</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>第一二排之间 · 第 1 列走道</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R1_C2</t>
+          <t>AISLE_R1_C1</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -25416,7 +25605,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>第一二排之间 · 第 2 列走道</t>
+          <t>第一二排之间 · 第 1 列走道</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -25425,7 +25614,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R1_C3</t>
+          <t>AISLE_R1_C2</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -25435,7 +25624,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>第一二排之间 · 第 3 列走道</t>
+          <t>第一二排之间 · 第 2 列走道</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -25444,7 +25633,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R2_C1</t>
+          <t>AISLE_R1_C3</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -25454,7 +25643,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>第三四排之间 · 第 1 列走道</t>
+          <t>第一二排之间 · 第 3 列走道</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -25463,7 +25652,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R2_C2</t>
+          <t>AISLE_R2_C1</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -25473,7 +25662,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>第三四排之间 · 第 2 列走道</t>
+          <t>第三四排之间 · 第 1 列走道</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -25482,7 +25671,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R2_C3</t>
+          <t>AISLE_R2_C2</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -25492,7 +25681,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>第三四排之间 · 第 3 列走道</t>
+          <t>第三四排之间 · 第 2 列走道</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -25501,17 +25690,17 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>BACK_LEFT</t>
+          <t>AISLE_R2_C3</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>aisle</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>后墙前 · 左</t>
+          <t>第三四排之间 · 第 3 列走道</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -25520,7 +25709,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>BACK_MID</t>
+          <t>BACK_LEFT</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -25530,7 +25719,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>后墙前 · 中（板报 / 储物柜一侧）</t>
+          <t>后墙前 · 左</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -25539,7 +25728,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>BACK_RIGHT</t>
+          <t>BACK_MID</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -25549,7 +25738,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>后墙前 · 右</t>
+          <t>后墙前 · 中（板报 / 储物柜一侧）</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -25558,17 +25747,17 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>SIDE_LEFT</t>
+          <t>BACK_RIGHT</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>左侧墙 · 窗边</t>
+          <t>后墙前 · 右</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -25577,7 +25766,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SIDE_RIGHT</t>
+          <t>SIDE_LEFT</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -25587,7 +25776,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>右侧墙边</t>
+          <t>左侧墙 · 窗边</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -25596,17 +25785,17 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PODIUM_LEFT</t>
+          <t>SIDE_RIGHT</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>podium</t>
+          <t>side</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>讲台前 · 左</t>
+          <t>右侧墙边</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -25615,7 +25804,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>PODIUM_RIGHT</t>
+          <t>PODIUM_LEFT</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -25625,99 +25814,94 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>讲台前 · 右</t>
+          <t>讲台前 · 左</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
       <c r="E49" s="6" t="inlineStr"/>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>PODIUM_RIGHT</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>podium</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>讲台前 · 右</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>移动与导航参数 —— data/rules/movement.csv</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>param</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>新值／改动（填写）</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>备注（填写）</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>leave_decide_interval_seconds</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>每段课间段首判定一次离座；50 秒后再判定一次；事件结束不追加判定</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr"/>
-      <c r="F53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>meters_per_tick</t>
+          <t>leave_decide_interval_seconds</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>m/tick</t>
+          <t>s</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>每 tick 移动距离；0.8 米 / 秒 ≈ 跨一排 2 秒、横穿教室 9.4 米约 12 秒；与上课归位隐含速度（约 0.76 米 / 秒）趋于一致（2026-10-08 由 0.13 上调）</t>
+          <t>每段课间段首判定一次离座；50 秒后再判定一次；事件结束不追加判定</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr"/>
@@ -25726,22 +25910,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>player_radius</t>
+          <t>meters_per_tick</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m/tick</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>玩家碰撞半径;避障时把桌椅矩形外扩这个距离(人物中心不得进入)</t>
+          <t>每 tick 移动距离；0.8 米 / 秒 ≈ 跨一排 2 秒、横穿教室 9.4 米约 12 秒；与上课归位隐含速度（约 0.76 米 / 秒）趋于一致（2026-10-08 由 0.13 上调）</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr"/>
@@ -25750,12 +25934,12 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>walk_epsilon</t>
+          <t>player_radius</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -25765,7 +25949,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>到位判定容差</t>
+          <t>玩家碰撞半径;避障时把桌椅矩形外扩这个距离(人物中心不得进入)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr"/>
@@ -25774,12 +25958,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>nav_grid_size</t>
+          <t>walk_epsilon</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -25789,7 +25973,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>寻路网格边长（A* 用）；玩家路线与 WASD 采样步长都取它的一半；越小越精细也越慢</t>
+          <t>到位判定容差</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr"/>
@@ -25798,12 +25982,12 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>stand_snap_radius</t>
+          <t>nav_grid_size</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -25813,7 +25997,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>点地面时的站立点吸附半径；此半径内有合法且空闲的站立点就吸附过去</t>
+          <t>寻路网格边长（A* 用）；玩家路线与 WASD 采样步长都取它的一半；越小越精细也越慢</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr"/>
@@ -25822,12 +26006,12 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>nav_cell_size</t>
+          <t>stand_snap_radius</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -25837,7 +26021,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>导航网格 cell_size；须与 resources/navigation/classroom_nav.tres 一致（行间过道净宽只有 0.66 米，网格要够细）</t>
+          <t>点地面时的站立点吸附半径；此半径内有合法且空闲的站立点就吸附过去</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr"/>
@@ -25846,12 +26030,12 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>nav_agent_height</t>
+          <t>nav_cell_size</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -25861,7 +26045,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>导航网格 agent_height；须与烘焙产物一致；大于人物视觉高 1.35、小于层高 3.46</t>
+          <t>导航网格 cell_size；须与 resources/navigation/classroom_nav.tres 一致（行间过道净宽只有 0.66 米，网格要够细）</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr"/>
@@ -25870,12 +26054,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>nav_max_climb</t>
+          <t>nav_agent_height</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -25885,7 +26069,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>导航网格 agent_max_climb；**必须显著小于 nav_blocker_height**，否则 Recast 会把桌顶面与地面判为连通（人物会沿导航“走上桌子”）</t>
+          <t>导航网格 agent_height；须与烘焙产物一致；大于人物视觉高 1.35、小于层高 3.46</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr"/>
@@ -25894,12 +26078,12 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>nav_blocker_height</t>
+          <t>nav_max_climb</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -25909,7 +26093,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>桌椅阻挡盒高度（米）；须 ≥ 桌面实际高度 0.74 且 &gt; nav_max_climb；由 tools/bake_classroom_nav.gd 与场景校验共同锁住</t>
+          <t>导航网格 agent_max_climb；**必须显著小于 nav_blocker_height**，否则 Recast 会把桌顶面与地面判为连通（人物会沿导航“走上桌子”）</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
@@ -25918,12 +26102,12 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>nav_path_epsilon</t>
+          <t>nav_blocker_height</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -25933,11 +26117,35 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>判定「点是否落在导航面上 / 路径末点是否到达目标」的容差</t>
+          <t>桌椅阻挡盒高度（米）；须 ≥ 桌面实际高度 0.74 且 &gt; nav_max_climb；由 tools/bake_classroom_nav.gd 与场景校验共同锁住</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr"/>
       <c r="F63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>nav_path_epsilon</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>判定「点是否落在导航面上 / 路径末点是否到达目标」的容差</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26090,7 +26298,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>study_together|pass_note|stress_drip|transmission</t>
+          <t>pass_note|stress_drip|transmission</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -26168,7 +26376,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>study_together|pass_note|stress_drip|transmission</t>
+          <t>pass_note|stress_drip|transmission</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -28927,7 +29135,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>现状：已实装玩家侧（2026-10-10；NPC 侧仍是「空闲即在学」） ｜ 只读列不要改；请在「新值／改动（填写）」列写本次大调整</t>
+          <t>现状：已实装（2026-10-10：玩家主动 + NPC 概率决策 + 学习圈结算） ｜ 只读列不要改；请在「新值／改动（填写）」列写本次大调整</t>
         </is>
       </c>
     </row>

--- a/docs/design/行为事件表.xlsx
+++ b/docs/design/行为事件表.xlsx
@@ -20077,7 +20077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -20117,7 +20117,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>全部效果行（43 条）</t>
+          <t>全部效果行（47 条）</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -22705,112 +22705,215 @@
       <c r="L46" s="6" t="inlineStr"/>
       <c r="M46" s="6" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>leave_absence</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>affinity</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>邻居对出门玩家的好感代价</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>leave_class</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr"/>
+      <c r="M47" s="6" t="inlineStr"/>
+    </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>P0 待创建效果行（尚未落 data/balance/w_events.csv；来源 §17.2.5、§17.3.5）</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n"/>
-      <c r="L48" s="4" t="n"/>
-      <c r="M48" s="4" t="n"/>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>teacher_visit_stress</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>0.425</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>0.425</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>老师到场压力（学习睡觉缺席豁免）</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>teacher_patrol</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr"/>
+      <c r="M48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>axis</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>w_e</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>w_s</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>w_f</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>w_j</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>归属行为</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>新值／改动（填写）</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>备注（填写）</t>
-        </is>
-      </c>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>ask_question</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>提问：对方对玩家的信任增加（§18.2；坐 P0 时调用方再乘 emperor_bonus）</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="6" t="inlineStr"/>
+      <c r="M49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>teacher_visit_stress</t>
+          <t>teach_lesson</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
           <t>normal</t>
@@ -22818,165 +22921,118 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>老师巡查到场：全班压力 +3（豁免 睡觉 / 正在学习 / 出门）</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>teacher_patrol</t>
-        </is>
-      </c>
+          <t>讲题：玩家对对方的信任增加（§18.2；坐 P0 时调用方再乘 emperor_bonus）</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="6" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr"/>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>leave_absence</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>affinity</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>出门：8 邻域邻居对玩家好感 −3（常规档上限）</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>leave_class</t>
-        </is>
-      </c>
-      <c r="L51" s="6" t="inlineStr"/>
-      <c r="M51" s="6" t="inlineStr"/>
-    </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>study_stress</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>学习每 10 tick 结算：本人压力 +3（本次调整，改造原涓流 +1/每天 2 次）</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>study</t>
-        </is>
-      </c>
-      <c r="L52" s="6" t="inlineStr"/>
-      <c r="M52" s="6" t="inlineStr"/>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>P0 待创建效果行（尚未落 data/balance/w_events.csv；来源 §17.2.5、§17.3.5）</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>study_together_trust</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr"/>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>学习圈每 20 tick：双向信任 +1（替换 v4 §2.3 的「每天 2 次 A+1/T+1」）</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>study（学习圈）</t>
-        </is>
-      </c>
-      <c r="L53" s="6" t="inlineStr"/>
-      <c r="M53" s="6" t="inlineStr"/>
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>w_e</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>w_s</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>w_f</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>w_j</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>归属行为</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>新值／改动（填写）</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>备注（填写）</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>study_together_affinity</t>
+          <t>teacher_visit_stress</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
@@ -22990,17 +23046,17 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>学习圈每 20 tick：双向好感 +1</t>
+          <t>老师巡查到场：全班压力 +3（豁免 睡觉 / 正在学习 / 出门）</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>study（学习圈）</t>
+          <t>teacher_patrol</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr"/>
@@ -23009,17 +23065,17 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>study_together_stress</t>
+          <t>leave_absence</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr"/>
@@ -23033,17 +23089,17 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>学习圈每 20 tick：本人压力 +1</t>
+          <t>出门：8 邻域邻居对玩家好感 −3（常规档上限）</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>study（学习圈）</t>
+          <t>leave_class</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr"/>
@@ -23052,7 +23108,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>reject_stress（复用现有键）</t>
+          <t>study_stress</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -23062,7 +23118,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr"/>
@@ -23076,12 +23132,12 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>拒绝学习邀请：发起者压力 +2（复用现有 reject_stress，不新建键）</t>
+          <t>学习每 10 tick 结算：本人压力 +3（本次调整，改造原涓流 +1/每天 2 次）</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -23091,6 +23147,178 @@
       </c>
       <c r="L56" s="6" t="inlineStr"/>
       <c r="M56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>study_together_trust</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>学习圈每 20 tick：双向信任 +1（替换 v4 §2.3 的「每天 2 次 A+1/T+1」）</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>study（学习圈）</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr"/>
+      <c r="M57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>study_together_affinity</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>affinity</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>学习圈每 20 tick：双向好感 +1</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>study（学习圈）</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr"/>
+      <c r="M58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>study_together_stress</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>学习圈每 20 tick：本人压力 +1</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>study（学习圈）</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr"/>
+      <c r="M59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>reject_stress（复用现有键）</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>拒绝学习邀请：发起者压力 +2（复用现有 reject_stress，不新建键）</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr"/>
+      <c r="M60" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23103,7 +23331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23127,7 +23355,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>全部参数（20 条）</t>
+          <t>全部参数（23 条）</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -23541,6 +23769,63 @@
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>music_p</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>听音乐</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>snack_p</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>吃零食</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>book_p</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>看课外书</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24712,7 +24997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -24866,12 +25151,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>seat_zone_radius_m</t>
+          <t>seated_chat_range_m</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -24881,7 +25166,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>自己座位的范围半径：只有在这个范围内才算「在自己的座位上」（§8.23 学习等行为的硬前置）</t>
+          <t>同列前后紧邻且都在本座位时允许转身聊天的距离上限</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
@@ -24890,12 +25175,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>seated_chat_range_m</t>
+          <t>range_step_m</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -24905,7 +25190,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>同列前后紧邻且都在本座位时允许转身聊天的距离上限</t>
+          <t>连线阻挡判定采样步长（短连接段不得穿过桌椅）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -24914,22 +25199,18 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>range_step_m</t>
+          <t>clue_opacity_split</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>连线阻挡判定采样步长（短连接段不得穿过桌椅）</t>
+          <t>透明度分界：闲聊对象 O &lt; 该值透露 1 条，O ≥ 该值透露 2 条（§10.5）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
@@ -24938,18 +25219,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>clue_opacity_split</t>
+          <t>clue_count_low</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>条</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>透明度分界：闲聊对象 O &lt; 该值透露 1 条，O ≥ 该值透露 2 条（§10.5）</t>
+          <t>低透明度时透露的线索条数</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
@@ -24958,12 +25243,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>clue_count_low</t>
+          <t>clue_count_high</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -24973,7 +25258,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>低透明度时透露的线索条数</t>
+          <t>高透明度时透露的线索条数</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
@@ -24982,7 +25267,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>clue_count_high</t>
+          <t>actor_pick_layer</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -24990,14 +25275,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>条</t>
-        </is>
-      </c>
+      <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>高透明度时透露的线索条数</t>
+          <t>人物拾取体所在 3D 物理层（位掩码；地面点击不进这一层）</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
@@ -25006,117 +25287,126 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>actor_pick_layer</t>
+          <t>world_pick_blocker_layer</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>人物拾取体所在 3D 物理层（位掩码；地面点击不进这一层）</t>
+          <t>世界静态遮挡体所在 3D 物理层（桌椅 / 墙；挡住人物则不可选中）</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
       <c r="F13" s="6" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>world_pick_blocker_layer</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>世界静态遮挡体所在 3D 物理层（桌椅 / 墙；挡住人物则不可选中）</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>座位表（空间层） —— data/rules/seats.csv</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>座位表（空间层） —— data/rules/seats.csv</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>seat_id</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>col</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>新值／改动（填写）</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>备注（填写）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>seat_id</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>col</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>kind</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>新值／改动（填写）</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>备注（填写）</t>
-        </is>
-      </c>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>desk_side</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>讲桌旁：老师眼皮底下，邻居仅第一排 3 人</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>desk_side</t>
+          <t>grid</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>讲桌旁：老师眼皮底下，邻居仅第一排 3 人</t>
+          <t>第一排</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
@@ -25125,7 +25415,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -25135,7 +25425,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -25154,7 +25444,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -25164,7 +25454,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -25183,7 +25473,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -25193,7 +25483,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -25212,17 +25502,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -25230,18 +25520,14 @@
           <t>grid</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>第一排</t>
-        </is>
-      </c>
+      <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -25251,7 +25537,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -25266,7 +25552,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -25276,7 +25562,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -25291,7 +25577,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -25301,7 +25587,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -25316,17 +25602,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -25341,7 +25627,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -25351,7 +25637,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -25366,7 +25652,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -25376,7 +25662,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -25391,7 +25677,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -25401,7 +25687,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -25416,17 +25702,17 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -25434,14 +25720,18 @@
           <t>grid</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>最后一排</t>
+        </is>
+      </c>
       <c r="F30" s="6" t="inlineStr"/>
       <c r="G30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -25451,7 +25741,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -25470,7 +25760,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -25480,7 +25770,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -25499,7 +25789,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -25509,7 +25799,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -25525,77 +25815,67 @@
       <c r="F33" s="6" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>grid</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>最后一排</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr"/>
-      <c r="G34" s="6" t="inlineStr"/>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>站立点（空闲站立位置） —— data/rules/stand_points.csv</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>站立点（空闲站立位置） —— data/rules/stand_points.csv</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>point_id</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>新值／改动（填写）</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>备注（填写）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>point_id</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>kind</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>新值／改动（填写）</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>备注（填写）</t>
-        </is>
-      </c>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>AISLE_R1_C1</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>aisle</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>第一二排之间 · 第 1 列走道</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R1_C1</t>
+          <t>AISLE_R1_C2</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -25605,7 +25885,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>第一二排之间 · 第 1 列走道</t>
+          <t>第一二排之间 · 第 2 列走道</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -25614,7 +25894,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R1_C2</t>
+          <t>AISLE_R1_C3</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -25624,7 +25904,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>第一二排之间 · 第 2 列走道</t>
+          <t>第一二排之间 · 第 3 列走道</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -25633,7 +25913,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R1_C3</t>
+          <t>AISLE_R2_C1</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -25643,7 +25923,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>第一二排之间 · 第 3 列走道</t>
+          <t>第三四排之间 · 第 1 列走道</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -25652,7 +25932,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R2_C1</t>
+          <t>AISLE_R2_C2</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -25662,7 +25942,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>第三四排之间 · 第 1 列走道</t>
+          <t>第三四排之间 · 第 2 列走道</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -25671,7 +25951,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R2_C2</t>
+          <t>AISLE_R2_C3</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -25681,7 +25961,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>第三四排之间 · 第 2 列走道</t>
+          <t>第三四排之间 · 第 3 列走道</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -25690,17 +25970,17 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>AISLE_R2_C3</t>
+          <t>BACK_LEFT</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>aisle</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>第三四排之间 · 第 3 列走道</t>
+          <t>后墙前 · 左</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -25709,7 +25989,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>BACK_LEFT</t>
+          <t>BACK_MID</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -25719,7 +25999,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>后墙前 · 左</t>
+          <t>后墙前 · 中（板报 / 储物柜一侧）</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -25728,7 +26008,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>BACK_MID</t>
+          <t>BACK_RIGHT</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -25738,7 +26018,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>后墙前 · 中（板报 / 储物柜一侧）</t>
+          <t>后墙前 · 右</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -25747,17 +26027,17 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>BACK_RIGHT</t>
+          <t>SIDE_LEFT</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>side</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>后墙前 · 右</t>
+          <t>左侧墙 · 窗边</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -25766,7 +26046,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SIDE_LEFT</t>
+          <t>SIDE_RIGHT</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -25776,7 +26056,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>左侧墙 · 窗边</t>
+          <t>右侧墙边</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -25785,17 +26065,17 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>SIDE_RIGHT</t>
+          <t>PODIUM_LEFT</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>podium</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>右侧墙边</t>
+          <t>讲台前 · 左</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -25804,7 +26084,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>PODIUM_LEFT</t>
+          <t>PODIUM_RIGHT</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -25814,94 +26094,99 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>讲台前 · 左</t>
+          <t>讲台前 · 右</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
       <c r="E49" s="6" t="inlineStr"/>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>PODIUM_RIGHT</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>podium</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>讲台前 · 右</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr"/>
-      <c r="E50" s="6" t="inlineStr"/>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>移动与导航参数 —— data/rules/movement.csv</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>移动与导航参数 —— data/rules/movement.csv</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>新值／改动（填写）</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>备注（填写）</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>param</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>新值／改动（填写）</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>备注（填写）</t>
-        </is>
-      </c>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>leave_decide_interval_seconds</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>每段课间段首判定一次离座；50 秒后再判定一次；事件结束不追加判定</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>leave_decide_interval_seconds</t>
+          <t>meters_per_tick</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m/tick</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>每段课间段首判定一次离座；50 秒后再判定一次；事件结束不追加判定</t>
+          <t>每 tick 移动距离；1.6 米 / 秒 ≈ 跨一排 1 秒、横穿教室 9.4 米约 6 秒（2026-10-12 由 0.8 上调，用户裁定原速太慢；上课归位自 2026-10-11 起为黑幕内瞬移，不再有对应速度）</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr"/>
@@ -25910,22 +26195,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>meters_per_tick</t>
+          <t>player_radius</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>m/tick</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>每 tick 移动距离；0.8 米 / 秒 ≈ 跨一排 2 秒、横穿教室 9.4 米约 12 秒；与上课归位隐含速度（约 0.76 米 / 秒）趋于一致（2026-10-08 由 0.13 上调）</t>
+          <t>玩家碰撞半径;避障时把桌椅矩形外扩这个距离(人物中心不得进入)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr"/>
@@ -25934,12 +26219,12 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>player_radius</t>
+          <t>walk_epsilon</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -25949,7 +26234,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>玩家碰撞半径;避障时把桌椅矩形外扩这个距离(人物中心不得进入)</t>
+          <t>到位判定容差</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr"/>
@@ -25958,12 +26243,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>walk_epsilon</t>
+          <t>nav_grid_size</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -25973,7 +26258,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>到位判定容差</t>
+          <t>寻路网格边长（A* 用）；玩家路线与 WASD 采样步长都取它的一半；越小越精细也越慢</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr"/>
@@ -25982,12 +26267,12 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>nav_grid_size</t>
+          <t>stand_snap_radius</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -25997,7 +26282,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>寻路网格边长（A* 用）；玩家路线与 WASD 采样步长都取它的一半；越小越精细也越慢</t>
+          <t>点地面时的站立点吸附半径；此半径内有合法且空闲的站立点就吸附过去</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr"/>
@@ -26006,12 +26291,12 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>stand_snap_radius</t>
+          <t>nav_cell_size</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -26021,7 +26306,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>点地面时的站立点吸附半径；此半径内有合法且空闲的站立点就吸附过去</t>
+          <t>导航网格 cell_size；须与 resources/navigation/classroom_nav.tres 一致（行间过道净宽只有 0.66 米，网格要够细）</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr"/>
@@ -26030,12 +26315,12 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>nav_cell_size</t>
+          <t>nav_agent_height</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -26045,7 +26330,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>导航网格 cell_size；须与 resources/navigation/classroom_nav.tres 一致（行间过道净宽只有 0.66 米，网格要够细）</t>
+          <t>导航网格 agent_height；须与烘焙产物一致；大于人物视觉高 1.35、小于层高 3.46</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr"/>
@@ -26054,12 +26339,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>nav_agent_height</t>
+          <t>nav_max_climb</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -26069,7 +26354,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>导航网格 agent_height；须与烘焙产物一致；大于人物视觉高 1.35、小于层高 3.46</t>
+          <t>导航网格 agent_max_climb；**必须显著小于 nav_blocker_height**，否则 Recast 会把桌顶面与地面判为连通（人物会沿导航“走上桌子”）</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr"/>
@@ -26078,12 +26363,12 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>nav_max_climb</t>
+          <t>nav_blocker_height</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -26093,7 +26378,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>导航网格 agent_max_climb；**必须显著小于 nav_blocker_height**，否则 Recast 会把桌顶面与地面判为连通（人物会沿导航“走上桌子”）</t>
+          <t>桌椅阻挡盒高度（米）；须 ≥ 桌面实际高度 0.74 且 &gt; nav_max_climb；由 tools/bake_classroom_nav.gd 与场景校验共同锁住</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
@@ -26102,12 +26387,12 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>nav_blocker_height</t>
+          <t>nav_path_epsilon</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -26117,35 +26402,11 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>桌椅阻挡盒高度（米）；须 ≥ 桌面实际高度 0.74 且 &gt; nav_max_climb；由 tools/bake_classroom_nav.gd 与场景校验共同锁住</t>
+          <t>判定「点是否落在导航面上 / 路径末点是否到达目标」的容差</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr"/>
       <c r="F63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>nav_path_epsilon</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>判定「点是否落在导航面上 / 路径末点是否到达目标」的容差</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr"/>
-      <c r="F64" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26158,7 +26419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -26541,183 +26802,173 @@
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="6" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>study_speed_interval_seconds</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>连续学习每满这些现实秒提升一档；暂停不累计</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+    </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>study_speed_step</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>每档增加的世界时间倍率；不封顶</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>时间运行时参数 —— data/rules/time_runtime.csv</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>新值／改动（填写）</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>备注（填写）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>term_days</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>学期长度（天）：第 30 天结束后停止模拟，不给可操作的第 31 天</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>max_ticks_per_frame</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>每帧最多补的模拟 tick 数（性能预算，不影响 tick 总数；积压保留、禁止跳 tick）</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>时间呈现参数 —— data/rules/time_presentation.csv</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>phase_id</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>display_name</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>real_duration_seconds</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>game_duration_seconds</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>新值／改动（填写）</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>备注（填写）</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>morning_break</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>上午课间</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>morning_class</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>上午课堂</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>lunch_break</t>
+          <t>morning_break</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>中午午休</t>
+          <t>上午课间</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -26736,12 +26987,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>afternoon_class</t>
+          <t>morning_class</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>下午课堂</t>
+          <t>上午课堂</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -26760,12 +27011,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>afternoon_break</t>
+          <t>lunch_break</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>下午课间</t>
+          <t>中午午休</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -26784,26 +27035,74 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>day_settle</t>
+          <t>afternoon_class</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>今日结算</t>
+          <t>下午课堂</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>afternoon_break</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>下午课间</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>day_settle</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>今日结算</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28759,7 +29058,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>**待建**</t>
+          <t>已存在</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -28778,7 +29077,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>**待建**</t>
+          <t>已存在</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -28797,7 +29096,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>**待建**</t>
+          <t>已存在</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -29816,7 +30115,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>不在座位时先走回座位（走动 0.8 m/tick）；坐下为姿态准备；**走动与准备都不产生成绩**</t>
+          <t>不在座位时先走回座位（走动 1.6 m/tick）；坐下为姿态准备；**走动与准备都不产生成绩**</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -32443,7 +32742,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>部分实现：玩家移动与占用互斥已通；NPC 移动耗时仍只用于表现层归位</t>
+          <t>部分实现：玩家移动与占用互斥已通；上课归位为黑幕内瞬移贴座（2026-10-12），NPC 移动耗时未进内核</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -32530,7 +32829,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>改变临时位置（互动距离与活动圈以 position 为准），段末回座位</t>
+          <t>改变临时位置（互动距离与活动圈以 position 为准），段末回座位（上课相位为黑幕内瞬移贴座）</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -32911,7 +33210,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>按距离：ceil(路径长度 / meters_per_tick)；速度 0.8 m/tick。behaviors.csv 现值 15 仅代表表现层归位时限</t>
+          <t>按距离：ceil(路径长度 / meters_per_tick)；速度 1.6 m/tick。behaviors.csv 现值 15 暂无消费者（上课归位已改为黑幕内瞬移贴座）</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -33341,7 +33640,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>沿路线行走，速度 0.8 m/tick</t>
+          <t>沿路线行走，速度 1.6 m/tick</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -35900,7 +36199,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>无独立计时；走动按距离另算（0.8 m/tick）</t>
+          <t>无独立计时；走动按距离另算（1.6 m/tick）</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
